--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_supneta_a_2019_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_supneta_a_2019_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:03</t>
+    <t xml:space="preserve">2026-09-24 00:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -684,7 +684,7 @@
         <v>-0.24</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0.09</v>
@@ -704,13 +704,13 @@
         <v>21</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.38</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="10">
@@ -727,13 +727,13 @@
         <v>21</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="11">
@@ -744,19 +744,19 @@
         <v>16</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>21</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="12">
@@ -796,13 +796,13 @@
         <v>21</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.13</v>
+        <v>0.07</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="14">
@@ -819,13 +819,13 @@
         <v>21</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="15">
@@ -845,10 +845,10 @@
         <v>0.21</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="16">
